--- a/new updates/java_interviews_updated (version 1).xlsx
+++ b/new updates/java_interviews_updated (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamalasekaran.s\Documents\workspace_updated\event-ledger-api\new updates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamalasekaran.s\Documents\Preparation\study material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3900A295-425D-43FC-8632-8F4606618287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF835831-0B19-4B63-9664-BE5B23BB4D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="12" activeTab="15" xr2:uid="{06F0298F-39CB-45B1-A366-BCCF7240D96A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="15" activeTab="15" xr2:uid="{06F0298F-39CB-45B1-A366-BCCF7240D96A}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="18" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="2169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="2201">
   <si>
     <t>Life cycle of Thread</t>
   </si>
@@ -25101,9 +25101,6 @@
     <t>How do you identify whether the bottleneck is Java, DB, Kafka or network</t>
   </si>
   <si>
-    <t>Java concurrency → Spring transactions → REST/idempotency → Microservice design → Kafka → Saga/Outbox → DB locking → Resilience4j → Security → Production troubleshooting → System design</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Publisher, published the message and it is not saved in publisher DB due to db outage. Now How do you maintain data consistency between services(publisher/consumer).</t>
   </si>
   <si>
@@ -25114,6 +25111,1663 @@
   </si>
   <si>
     <t>Three types of design pattern categorization</t>
+  </si>
+  <si>
+    <t>Java concurrency → Spring transactions → REST/idempotency → 
+Microservice design → Kafka → Saga/Outbox → DB locking → Resilience4j → Security → Production troubleshooting → System design</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ConcurrentHashMap:
+     -- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Multithreaded, multiple thread access same resource for read/write
+    -- to avoid cuncurrentmodification exception(Fail-safe)
+     --  It also provides atomic compound operations such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>putIfAbsent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>computeIfAbsent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, compute, and merge, compute, and merge</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     -- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lock only segment not entire thread (bucket)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    -- Using CAS (Compare and Swap)
+                     Change the value only if it is still the value I expected
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>if (currentValue == expectedValue)
+    currentValue = newValue
+    return true
+else
+    return false;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CAS (Compare-And-Swap) is a lock-free atomic operation used heavily in Java concurrency.
+The idea is:
+"Change the value only if it is still the value I expected
+CAS(memoryLocation, expectedValue, newValue)
+if (currentValue == expectedValue)
+    currentValue = newValue
+    return true
+else
+    return false
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AtomicInteger uses CAS internally for Counter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>volatile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> provides visibility but not atomicity. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>synchronized</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> provides both visibility and mutual exclusion, allowing multiple operations to be executed as one critical section. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Atomic classes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> such as AtomicInteger provide atomic operations using lock-free mechanisms such as CAS, making them suitable for simple concurrent state updates like counters. For complex operations involving multiple variables or business invariants, I would prefer synchronized or an appropriate locking mechanism rather than relying on a single atomic variable
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>One-line memory trick
+volatile → visibility
+synchronized → visibility + locking + atomic critical section
+Atomic → atomic operations + CAS + usually non-blockin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>g</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If you mean CompletableFuture in Java, it is Java's API for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>asynchronous, non-blocking computation and composing multiple async operations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+java.util.concurrent.CompletableFuture
+CompletableFuture represents the result of an asynchronous computation. An async task can be submitted using runAsync or supplyAsync, and dependent operations can be composed using methods such as thenApply, thenCompose, and thenCombine. Completion stages are triggered when the previous stage completes, and exceptions can be handled using exceptionally, handle, or whenComplete. By default, async operations use the common ForkJoinPool unless an explicit Executor is supplied. In production Spring Boot applications, I prefer a properly sized and monitored custom executor, especially for blocking I/O.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CompletableFuture represents the result of an asynchronous computation. An async task can be submitted using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>runAsync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supplyAsync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and dependent operations can be composed using methods such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thenApply</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thenCompose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thenCombine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Completion stages are triggered when the previous stage completes, and exceptions can be handled using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exceptionally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>handle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>whenComplete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. By default, async operations use the common </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ForkJoinPool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unless an explicit Executor is supplied. In production Spring Boot applications, I prefer a properly sized and monitored custom executor, especially for blocking I/O.</t>
+    </r>
+  </si>
+  <si>
+    <t>Two payment requests arrives at the same time. How do you prevent double payment across microservices</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - Don’t rely on application level locking using syncronized since microservice architecture different pods will be configured.
+ - This will produce RACE problem
+- Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Idempotency-- Idempotency key
+-- post: idemptency-key
+Request flow1:
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">receive &lt;&lt;idempotence key&gt;&gt;
+    inserts payment now.
+    charge customer. change status to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>success</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Request flow 2:
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">try to insert same key,
+    unique constraint fails
+    fetch existing payment , return existing response.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Alogrithm:
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">if payment fails with unique constraints, throws DuplicateKeyExceptions
+       catch it.
+If status is pending, don't go for poll the gateway or process the request
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Two payment requests arrives at the same time. What if server crashes</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Exponential back-off retries
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">correct approach : reconclilation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A background recovery job periodically checks old Pending payments. For example, 30 seconds</t>
+    </r>
+  </si>
+  <si>
+    <t>Order created, payment failed. How to maintain the consistency. Now the inventory is reserved and payment failed</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - @Transactional will not work here. Because it will suite for molothic appliction.
+Saga design Pattern:
+     - Order created through Kafka (or ) orchestrator.
+    - process payment-&gt; if payment failed(system will call the compensation service)
+           --&gt; release the inventory reserved. order status cancelled.
+    --&gt; order--&gt; created, inventory--&gt; blocked, payment--&gt;failed , (compensation), inventory--&gt;released, Order--&gt;cancelled.
+This is eventual consistency.
+Chereography :
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">service communicate through events
+     each service reacts independently
+    complex to debug, easy scalable.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Orchestrotro:
+     Central orchestrator controls the flow:
+           Orchestrator became centrol component.
+   Orchestrator handles business workflow:
+Calls services in the required sequence
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinates Saga
+Handles retries/timeouts
+Compensation
+Idempotency
+Workflow state</t>
+    </r>
+  </si>
+  <si>
+    <t>How to prevent cascading failures. What if one service is slow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First fix: timeouts(
+second fix: circuit breaker (bulkhead pattern)
+                              circuit breaker pattern (open, close, half-open)
+Third fix: retries(exponsential), based on the request response.
+              Use jitter, exponential backoff. limit retry count.
+fourth fix: bulkhead isolation:
+                             isolate the thread pool for each service. Not block the entire thread pool.
+</t>
+  </si>
+  <si>
+    <t>what happened when traffic spikes</t>
+  </si>
+  <si>
+    <t>Timelimiter, ratelimiter, retry,  circuit breaker, bulkhead</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">API latency increased--&gt; check p95/p96 --&gt; distributed trace--&gt; 
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --&gt; CPU/GC/Threads
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --&gt; SQL/locks/DB connection/sql latency
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kafka</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --&gt; consumer lag, Consumer throughput, consumer latency, producer latency, consumer rebalance, partition distribution, broker health
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>..(network)--&gt; network latency, throughput, load-balancer latency, service to service latency
+And correlate everything against the same timestamp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"First, I wouldn't assume that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adding pods will solve the problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I'd establish the scaling requirement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>using RPS, latency and resource utilization, and identify the current bottleneck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I'd ensure the Spring Boot service is stateless and horizontally scalable, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>then use Kubernetes HPA with CPU plus appropriate custom metrics such as RPS or queue depth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I'd configure proper </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>resource requests/limits, readiness probes and graceful shutdown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+Before going from 5 to 50 pods, I'd validate all shared dependencies. For example,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if each pod has 20 DB connections, 50 pods could potentially require 1,000 connections</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, which may overload the database. I'd similarly validate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kafka partition capacity, Redis throughput and downstream service capacity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I'd tune thread pools and connection pools accordingly.
+I'd perform load testing progressively from 5 to 50 pods and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>monitor p95/p99 latency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, error rate, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CPU, memory, DB connections, SQL latency, Kafka lag, Redis latency and downstream response times</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Finally, I'd distribute pods across availability zones using topology constraints and use PDBs for availability during node maintenance. So the objective isn't just scaling the application from 5 to 50 pods; it's scaling the entire dependency chain without creating a new bottleneck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  --&gt; Distingush b/w </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>local transaction consistency (use ACID @Transactional with appropriate isolation and propagation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), and distributed transaction consistency.
+ --&gt; For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>distributed transactions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, I avoid sharing a transaction across multiple databases and generally </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use the Saga pattern, where each service performs a local transaction and failures are handled through compensating actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+ --&gt; To guarantee consistency between database update and kafka event publishing, I </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">use Transactional Outbox pattern. Consumers are idempotent using unique event or transaction IDs
+  --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Concurrent updates are ensured using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">optimistic or pessimistic locking depending on contention.
+   --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I also use retries and DLT for transient message failures. 
+   --&gt; explicitly decide which data requires strong consistency and eventual consistency</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We need multiple layer of protection.
+     ---&gt; every transfer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gets a unique idempotency key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and I </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>enforce a database unique constraint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on the transaction ID.
+     --&gt;  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To handle concurrent debit requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, I use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>optimistic locking or pessimistic row locking depending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on account contention; for highly contentious financial balances, I would carefully consider row-level pessimistic locking.
+  --&gt; Commit should happen automically.
+  --&gt; For communication between microservices, I use the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Outbox pattern </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">so the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>database transaction and event publication cannot diverge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>consumers are idempotent because Kafka can redeliver events</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+  --&gt; If the client times out after a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>successful debit and retries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, the same idempotency key returns the original result rather than executing another debit.
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Idempotency--&gt; Unique DB Constraints--&gt; concurrency control--&gt; ACID Transaction--&gt; Outbox--&gt; Idempontent kafka consumer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outbox prevents "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB committed but event lost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"; idempotency prevents "event delivered twice".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I would maintain an Outbox table in the Shipment service's PostgreSQL database. When a shipment state changes, for example from CREATED to IN_TRANSIT, the state update and corresponding ShipmentInTransit event are persisted in the same @Transactional database transaction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I would not publish directly to Kafka from the business transaction. A separate Outbox publisher, or preferably </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Debezium CDC for a high-scale platform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, publishes the committed outbox events to Kafka. The event carries a unique event ID, and downstream consumers are idempotent using that ID and a database unique constraint. I'd also implement retry, exponential backoff and DLT for failures, and use shipmentId as the Kafka key when event ordering per shipment is required</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If Kafka is down in the Shipment Outbox architecture, the important point is:
+The Shipment transaction should continue to work; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the event should remain safely stored in the Outbox and be published when Kafka recovers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>If Kafka is down in the Shipment Outbox architecture, the important point is:
+The Shipment transaction should continue to work; the event should remain safely stored in</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the Outbox and be published when Kafka recov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"If the Shipment database is down, I would fail the business operation safely because the database is the source of truth and both the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shipment state and Outbox event must be persisted atomically</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I would not acknowledge the request or publish a ShipmentCreated event independently to Kafka. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The API would return a 503 for a transient outage, with appropriate client retry using the same idempotency key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. On the infrastructure side, I'd use database HA/failover, connection-pool timeouts and circuit breakers to prevent thread exhaustion. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If the database commits successfully but the response is lost, the same idempotency key ensures a retry doesn't create a duplicate shipment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."</t>
+    </r>
+  </si>
+  <si>
+    <t>For a Shipment / banking-style microservices system, I would design Saga so that each service owns its local transaction, and the overall business transaction is coordinated through events rather than a distributed database transaction
+Saga + Outbox + Kafka + Idempotency + Retry/DLT</t>
+  </si>
+  <si>
+    <t>Apply below for downstream failures:
+               ---&gt; Apply timeout
+               ---&gt; Retry + exponential backoff + jitter
+               --&gt; Circuit breaker
+               --&gt; Bulkhead pattern
+              --&gt; Async kafka whereever possiblt
+             --&gt; Outbox for reliable events
+             --&gt; saga compensation for business failure transaction</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This is a classic dual-write problem. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I wouldn't try to solve it by publishing first and then updating the DB. I would use the Outbox pattern</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. The publisher's business change and the Outbox record are committed atomically in its local database. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Outbox publisher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> then sends the event to Kafka. If Kafka succeeds but the publisher DB is unavailable while updating the Outbox status, the event remains in a retryable state and may be published again. Therefore, I make the consumer idempotent using a unique event ID. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The consumer processes the business update and records the processed event ID in the same local database transaction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If the duplicate event arrives, the unique event ID prevents duplicate processing. This gives us reliable eventual consistency without requiring distributed two-phase commit</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Confirm and compare before vs now. (API p50,p 95, p99) all request?, only one pod?, only certain data?, only after deployment, only during trafic spike. 5xx, timeouts, connection pools, db latency, gc, cpu
+2. Where these 5 seconds being spent--&gt; Serialization, db, downstream http, kafka, db, controller, gateway, network, dns
+3. Java/JVM--&gt; cpu 95%(indicate serilization, large json process, expensive loops, excessive concurrency) GC(GC pause, heap dump, (may be due to db connection issue)) then take thread dump(look for Waiting , runnable, blocked thread)
+4. Check kafka--&gt; producer latency, consumer lag, consumer processing time, broker health, under-replicated partition, partition distribution
+5. Finally check network--&gt; network latency/TCP / DNS/ Load balancer/service mesh/connection establishment</t>
+  </si>
+  <si>
+    <t>implement idempotency using a client-provided idempotency key for commands such as payment or shipment creation. I persist that key with a request hash, processing status and the original response, and enforce a unique constraint at the database level. The idempotency record, business operation and Outbox event are committed in the same local transaction. If the same request is retried, I return the previously stored result instead of executing the operation again. I also validate the request hash so that the same idempotency key cannot be reused for a different request. For Kafka consumers, I use a unique event ID and persist the processed-event record in the same transaction as the business update. This protects against client retries, concurrent requests, Kafka redelivery and service restarts."</t>
+  </si>
+  <si>
+    <t>I assume duplicate delivery is possible because Kafka provides at-least-once delivery in the typical consumer model. Every event carries a globally unique and stable event ID. The consumer maintains a processed-event table with a unique constraint on that ID. Within one local database transaction, I perform the business update and insert the processed-event record. If the same event arrives again, the unique constraint/idempotency check prevents the business operation from being executed twice. This also protects us when an Outbox publisher successfully sends to Kafka but fails before recording the publish status, because the event may be published again. For transient failures I retry with backoff, while poison messages eventually go to a DLT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Optimistic locking:
+           -- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Optimistic locking assumes that concurrent updates are unlikely. We maintain </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Version </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">column.
+         If the update count is 0, another transaction has already modified the record
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Use when:
+          Reads are much more frequent than writes
+            Conflicts are relatively rare
+            We don't want database locks held for long periods
+Pesimistic locking:
+                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Select ... for update
+          Other transactions attempting to modify the locked row must wait
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use when :
+             Concurrent updates are highly likely
+             The operation is financially critical
+             We must prevent two transactions from modifying the same row simultaneously</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT ... FOR UPDATE is used when I need to read a row and then modify it within the same transaction, while preventing another transaction from modifying that row concurrently.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pesimistic locking</t>
+    </r>
+  </si>
+  <si>
+    <t>option 1: pesimistic locking
+option 2: Optimistic locking (use version increment)
+option 3: atomic conditional update(update set balance = balance-amount and balance&gt;=amount;</t>
   </si>
 </sst>
 </file>
@@ -25830,7 +27484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -25936,9 +27590,6 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="77" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="79" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -25953,7 +27604,21 @@
     <xf numFmtId="0" fontId="85" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="86" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="59" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="76" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="80" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -26306,7 +27971,7 @@
       <c r="B2" s="10">
         <v>117</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="65" t="s">
         <v>1909</v>
       </c>
       <c r="D2" s="30"/>
@@ -26321,7 +27986,7 @@
       <c r="B3" s="10">
         <v>50</v>
       </c>
-      <c r="C3" s="47"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
@@ -26334,7 +27999,7 @@
       <c r="B4" s="10">
         <v>44</v>
       </c>
-      <c r="C4" s="47"/>
+      <c r="C4" s="65"/>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -26347,7 +28012,7 @@
       <c r="B5" s="10">
         <v>69</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="65" t="s">
         <v>1910</v>
       </c>
       <c r="D5" s="30"/>
@@ -26362,7 +28027,7 @@
       <c r="B6" s="10">
         <v>115</v>
       </c>
-      <c r="C6" s="47"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -26375,7 +28040,7 @@
       <c r="B7" s="10">
         <v>66</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="65" t="s">
         <v>1911</v>
       </c>
       <c r="D7" s="30"/>
@@ -26390,7 +28055,7 @@
       <c r="B8" s="10">
         <v>23</v>
       </c>
-      <c r="C8" s="47"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -26403,7 +28068,7 @@
       <c r="B9" s="10">
         <v>105</v>
       </c>
-      <c r="C9" s="47"/>
+      <c r="C9" s="65"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -26416,7 +28081,7 @@
       <c r="B10" s="10">
         <v>30</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="65" t="s">
         <v>1912</v>
       </c>
       <c r="D10" s="30"/>
@@ -26431,7 +28096,7 @@
       <c r="B11" s="10">
         <v>64</v>
       </c>
-      <c r="C11" s="47"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -26444,7 +28109,7 @@
       <c r="B12" s="35">
         <v>42</v>
       </c>
-      <c r="C12" s="47"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
@@ -26457,7 +28122,7 @@
       <c r="B13" s="10">
         <v>81</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="65" t="s">
         <v>1913</v>
       </c>
       <c r="D13" s="30"/>
@@ -26472,7 +28137,7 @@
       <c r="B14" s="10">
         <v>87</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
@@ -29683,1031 +31348,1150 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7958D73C-4C2C-47EE-B1B1-81B674AC1F18}">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="181" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="98.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="48" t="s">
         <v>2042</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>2040</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="48">
+    <row r="2" spans="1:3">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="47" t="s">
         <v>2041</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="48">
+    <row r="3" spans="1:3" ht="225">
+      <c r="A3" s="47">
         <v>2</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>2043</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="48">
+      <c r="C3" s="31" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="195">
+      <c r="A4" s="47">
         <v>3</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="47" t="s">
         <v>2045</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="48">
+      <c r="C4" s="12" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="180">
+      <c r="A5" s="47">
         <v>4</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="47" t="s">
         <v>2046</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="48">
+      <c r="C5" s="12" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="180">
+      <c r="A6" s="47">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>2047</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="48">
+      <c r="C6" s="12" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="120">
+      <c r="A7" s="47">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>2048</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="48">
+      <c r="C7" s="12" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="47">
         <v>7</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="48" t="s">
         <v>2049</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="48">
+    <row r="9" spans="1:3">
+      <c r="A9" s="47">
         <v>8</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="48" t="s">
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="48">
+    <row r="10" spans="1:3">
+      <c r="A10" s="47">
         <v>9</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>2051</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="48">
+    <row r="11" spans="1:3">
+      <c r="A11" s="47">
         <v>10</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>2052</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="48">
+    <row r="12" spans="1:3">
+      <c r="A12" s="47">
         <v>11</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>2044</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="48">
+    <row r="13" spans="1:3">
+      <c r="A13" s="47">
         <v>12</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>2053</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="48">
+    <row r="14" spans="1:3">
+      <c r="A14" s="47">
         <v>13</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="47" t="s">
         <v>2054</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="48">
+    <row r="15" spans="1:3">
+      <c r="A15" s="47">
         <v>14</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="47" t="s">
         <v>2055</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="48">
+    <row r="16" spans="1:3">
+      <c r="A16" s="47">
         <v>15</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>2056</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="48">
+      <c r="A17" s="47">
         <v>16</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="47" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="47">
+        <v>17</v>
+      </c>
+      <c r="B18" s="47" t="s">
         <v>2167</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="48">
+    <row r="19" spans="1:2">
+      <c r="A19" s="49" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="50">
+        <v>1</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="50">
+        <v>2</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="50">
+        <v>3</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="50">
+        <v>4</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="50">
+        <v>5</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="50">
+        <v>6</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="50">
+        <v>7</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="50">
+        <v>8</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="50">
+        <v>9</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="50">
+        <v>10</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="50">
+        <v>11</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="50">
+        <v>12</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="50">
+        <v>13</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="50">
+        <v>14</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="50">
+        <v>15</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="50">
+        <v>16</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="50">
         <v>17</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B36" s="50" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="50">
+        <v>18</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="50">
+        <v>19</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="50">
+        <v>20</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="51" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="52">
+        <v>1</v>
+      </c>
+      <c r="B41" s="52" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="52">
+        <v>2</v>
+      </c>
+      <c r="B42" s="52" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="52">
+        <v>3</v>
+      </c>
+      <c r="B43" s="52" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="52">
+        <v>4</v>
+      </c>
+      <c r="B44" s="52" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="52">
+        <v>5</v>
+      </c>
+      <c r="B45" s="52" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="52">
+        <v>6</v>
+      </c>
+      <c r="B46" s="52" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="52">
+        <v>7</v>
+      </c>
+      <c r="B47" s="52" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="52">
+        <v>8</v>
+      </c>
+      <c r="B48" s="51" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="52">
+        <v>9</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="52">
+        <v>10</v>
+      </c>
+      <c r="B50" s="52" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="52">
+        <v>11</v>
+      </c>
+      <c r="B51" s="52" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="52">
+        <v>12</v>
+      </c>
+      <c r="B52" s="52" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="52">
+        <v>13</v>
+      </c>
+      <c r="B53" s="51" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="52">
+        <v>14</v>
+      </c>
+      <c r="B54" s="52" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="52">
+        <v>15</v>
+      </c>
+      <c r="B55" s="52" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="53" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="54">
+        <v>1</v>
+      </c>
+      <c r="B57" s="54" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="54">
+        <v>2</v>
+      </c>
+      <c r="B58" s="54" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="54">
+        <v>3</v>
+      </c>
+      <c r="B59" s="53" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="54">
+        <v>4</v>
+      </c>
+      <c r="B60" s="54" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="54">
+        <v>5</v>
+      </c>
+      <c r="B61" s="54" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="54">
+        <v>6</v>
+      </c>
+      <c r="B62" s="54" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="54">
+        <v>7</v>
+      </c>
+      <c r="B63" s="54" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="54">
+        <v>8</v>
+      </c>
+      <c r="B64" s="54" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="54">
+        <v>9</v>
+      </c>
+      <c r="B65" s="54" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="54">
+        <v>10</v>
+      </c>
+      <c r="B66" s="54" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="54">
+        <v>11</v>
+      </c>
+      <c r="B67" s="54" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="55" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B68" s="55" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="56">
+        <v>1</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="56">
+        <v>2</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="56">
+        <v>3</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="56">
+        <v>4</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="56">
+        <v>5</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="56">
+        <v>6</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="56">
+        <v>7</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="56">
+        <v>8</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="56">
+        <v>9</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="56">
+        <v>10</v>
+      </c>
+      <c r="B78" s="56" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="56">
+        <v>11</v>
+      </c>
+      <c r="B79" s="56" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="56">
+        <v>12</v>
+      </c>
+      <c r="B80" s="56" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="56">
+        <v>13</v>
+      </c>
+      <c r="B81" s="56" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="56">
+        <v>14</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="56">
+        <v>15</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="56">
+        <v>16</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="56">
+        <v>17</v>
+      </c>
+      <c r="B85" s="56" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="56">
+        <v>18</v>
+      </c>
+      <c r="B86" s="56" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="56">
+        <v>19</v>
+      </c>
+      <c r="B87" s="56" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="56">
+        <v>20</v>
+      </c>
+      <c r="B88" s="56" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="30">
+      <c r="A89" s="56">
+        <v>21</v>
+      </c>
+      <c r="B89" s="62" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="57" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B90" s="57" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="240">
+      <c r="A91" s="58">
+        <v>1</v>
+      </c>
+      <c r="B91" s="58" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="60">
+      <c r="A92" s="58">
+        <v>2</v>
+      </c>
+      <c r="B92" s="58" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="60">
+      <c r="A93" s="58">
+        <v>3</v>
+      </c>
+      <c r="B93" s="58" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="58">
+        <v>4</v>
+      </c>
+      <c r="B94" s="58" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="58">
+        <v>5</v>
+      </c>
+      <c r="B95" s="58" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="58">
+        <v>6</v>
+      </c>
+      <c r="B96" s="58" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="58">
+        <v>7</v>
+      </c>
+      <c r="B97" s="58" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="58">
+        <v>8</v>
+      </c>
+      <c r="B98" s="58" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="58">
+        <v>9</v>
+      </c>
+      <c r="B99" s="58" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="58">
+        <v>10</v>
+      </c>
+      <c r="B100" s="58" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="58">
+        <v>11</v>
+      </c>
+      <c r="B101" s="58" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="58">
+        <v>12</v>
+      </c>
+      <c r="B102" s="58" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="58">
+        <v>13</v>
+      </c>
+      <c r="B103" s="58" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="58">
+        <v>14</v>
+      </c>
+      <c r="B104" s="58" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="58">
+        <v>15</v>
+      </c>
+      <c r="B105" s="58" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="59" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B106" s="59" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="60">
+        <v>1</v>
+      </c>
+      <c r="B107" s="63" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="150">
+      <c r="A108" s="60">
+        <v>2</v>
+      </c>
+      <c r="B108" s="63" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="180">
+      <c r="A109" s="60">
+        <v>2</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="60">
+        <v>3</v>
+      </c>
+      <c r="B110" s="60" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="60">
+        <v>4</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="60">
+        <v>5</v>
+      </c>
+      <c r="B112" s="60" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="60">
+        <v>6</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="60">
+        <v>7</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="60">
+        <v>8</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="135">
+      <c r="A116" s="60">
+        <v>9</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="150">
+      <c r="A117" s="60">
+        <v>10</v>
+      </c>
+      <c r="B117" s="60" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="120">
+      <c r="A118" s="60">
+        <v>11</v>
+      </c>
+      <c r="B118" s="60" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="60">
+      <c r="A119" s="60">
+        <v>12</v>
+      </c>
+      <c r="B119" s="60" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="75">
+      <c r="A120" s="60">
+        <v>13</v>
+      </c>
+      <c r="B120" s="60" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="165">
+      <c r="A121" s="60">
+        <v>14</v>
+      </c>
+      <c r="B121" s="60" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="60">
+      <c r="A122" s="60">
+        <v>15</v>
+      </c>
+      <c r="B122" s="60" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="120">
+      <c r="A123" s="60">
+        <v>16</v>
+      </c>
+      <c r="B123" s="60" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="210">
+      <c r="A124" s="60">
+        <v>17</v>
+      </c>
+      <c r="B124" s="60" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="180">
+      <c r="A125" s="60">
+        <v>18</v>
+      </c>
+      <c r="B125" s="60" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="285">
+      <c r="A126" s="60">
+        <v>19</v>
+      </c>
+      <c r="B126" s="60" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="120">
+      <c r="A127" s="60">
+        <v>20</v>
+      </c>
+      <c r="B127" s="60" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="45">
+      <c r="B128" s="64" t="s">
         <v>2168</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="50" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="51">
-        <v>1</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="51">
-        <v>2</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="51">
-        <v>3</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="51">
-        <v>4</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="51">
-        <v>5</v>
-      </c>
-      <c r="B24" s="51" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="51">
-        <v>6</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="51">
-        <v>7</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="51">
-        <v>8</v>
-      </c>
-      <c r="B27" s="51" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="51">
-        <v>9</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="51">
-        <v>10</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="51">
-        <v>11</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="51">
-        <v>12</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="51">
-        <v>13</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="51">
-        <v>14</v>
-      </c>
-      <c r="B33" s="51" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="51">
-        <v>15</v>
-      </c>
-      <c r="B34" s="51" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="51">
-        <v>16</v>
-      </c>
-      <c r="B35" s="51" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="51">
-        <v>17</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="51">
-        <v>18</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="51">
-        <v>19</v>
-      </c>
-      <c r="B38" s="51" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="51">
-        <v>20</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="52" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B40" s="52" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="53">
-        <v>1</v>
-      </c>
-      <c r="B41" s="53" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="53">
-        <v>2</v>
-      </c>
-      <c r="B42" s="53" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="53">
-        <v>3</v>
-      </c>
-      <c r="B43" s="53" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="53">
-        <v>4</v>
-      </c>
-      <c r="B44" s="53" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="53">
-        <v>5</v>
-      </c>
-      <c r="B45" s="53" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="53">
-        <v>6</v>
-      </c>
-      <c r="B46" s="53" t="s">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="53">
-        <v>7</v>
-      </c>
-      <c r="B47" s="53" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="53">
-        <v>8</v>
-      </c>
-      <c r="B48" s="52" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="53">
-        <v>9</v>
-      </c>
-      <c r="B49" s="53" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="53">
-        <v>10</v>
-      </c>
-      <c r="B50" s="53" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="53">
-        <v>11</v>
-      </c>
-      <c r="B51" s="53" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="53">
-        <v>12</v>
-      </c>
-      <c r="B52" s="53" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="53">
-        <v>13</v>
-      </c>
-      <c r="B53" s="52" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="53">
-        <v>14</v>
-      </c>
-      <c r="B54" s="53" t="s">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="53">
-        <v>15</v>
-      </c>
-      <c r="B55" s="53" t="s">
-        <v>2093</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="54" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B56" s="54" t="s">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="55">
-        <v>1</v>
-      </c>
-      <c r="B57" s="55" t="s">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="55">
-        <v>2</v>
-      </c>
-      <c r="B58" s="55" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="55">
-        <v>3</v>
-      </c>
-      <c r="B59" s="54" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="55">
-        <v>4</v>
-      </c>
-      <c r="B60" s="55" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="55">
-        <v>5</v>
-      </c>
-      <c r="B61" s="55" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="55">
-        <v>6</v>
-      </c>
-      <c r="B62" s="55" t="s">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="55">
-        <v>7</v>
-      </c>
-      <c r="B63" s="55" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="55">
-        <v>8</v>
-      </c>
-      <c r="B64" s="55" t="s">
-        <v>2102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="55">
-        <v>9</v>
-      </c>
-      <c r="B65" s="55" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="55">
-        <v>10</v>
-      </c>
-      <c r="B66" s="55" t="s">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="55">
-        <v>11</v>
-      </c>
-      <c r="B67" s="55" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="56" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B68" s="56" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="57">
-        <v>1</v>
-      </c>
-      <c r="B69" s="57" t="s">
-        <v>2106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="57">
-        <v>2</v>
-      </c>
-      <c r="B70" s="57" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="57">
-        <v>3</v>
-      </c>
-      <c r="B71" s="57" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="57">
-        <v>4</v>
-      </c>
-      <c r="B72" s="57" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="57">
-        <v>5</v>
-      </c>
-      <c r="B73" s="57" t="s">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="57">
-        <v>6</v>
-      </c>
-      <c r="B74" s="57" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="57">
-        <v>7</v>
-      </c>
-      <c r="B75" s="57" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="57">
-        <v>8</v>
-      </c>
-      <c r="B76" s="57" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="57">
-        <v>9</v>
-      </c>
-      <c r="B77" s="57" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="57">
-        <v>10</v>
-      </c>
-      <c r="B78" s="57" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="57">
-        <v>11</v>
-      </c>
-      <c r="B79" s="57" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="57">
-        <v>12</v>
-      </c>
-      <c r="B80" s="57" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="57">
-        <v>13</v>
-      </c>
-      <c r="B81" s="57" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="57">
-        <v>14</v>
-      </c>
-      <c r="B82" s="57" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="57">
-        <v>15</v>
-      </c>
-      <c r="B83" s="57" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="57">
-        <v>16</v>
-      </c>
-      <c r="B84" s="57" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="57">
-        <v>17</v>
-      </c>
-      <c r="B85" s="57" t="s">
-        <v>2122</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="57">
-        <v>18</v>
-      </c>
-      <c r="B86" s="57" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="57">
-        <v>19</v>
-      </c>
-      <c r="B87" s="57" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="57">
-        <v>20</v>
-      </c>
-      <c r="B88" s="57" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="57">
+    <row r="129" spans="1:3" ht="270">
+      <c r="A129" s="60">
         <v>21</v>
       </c>
-      <c r="B89" s="57" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="58" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B90" s="58" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="59">
-        <v>1</v>
-      </c>
-      <c r="B91" s="59" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="59">
-        <v>2</v>
-      </c>
-      <c r="B92" s="59" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="59">
-        <v>3</v>
-      </c>
-      <c r="B93" s="59" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="59">
-        <v>4</v>
-      </c>
-      <c r="B94" s="59" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="59">
-        <v>5</v>
-      </c>
-      <c r="B95" s="59" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="59">
-        <v>6</v>
-      </c>
-      <c r="B96" s="59" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="59">
-        <v>7</v>
-      </c>
-      <c r="B97" s="59" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="59">
-        <v>8</v>
-      </c>
-      <c r="B98" s="59" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="59">
-        <v>9</v>
-      </c>
-      <c r="B99" s="59" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="59">
-        <v>10</v>
-      </c>
-      <c r="B100" s="59" t="s">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="59">
-        <v>11</v>
-      </c>
-      <c r="B101" s="59" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="59">
-        <v>12</v>
-      </c>
-      <c r="B102" s="59" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="59">
-        <v>13</v>
-      </c>
-      <c r="B103" s="59" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="59">
-        <v>14</v>
-      </c>
-      <c r="B104" s="59" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="59">
-        <v>15</v>
-      </c>
-      <c r="B105" s="59" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="60" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B106" s="60" t="s">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="61">
-        <v>1</v>
-      </c>
-      <c r="B107" s="61" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="61">
-        <v>2</v>
-      </c>
-      <c r="B108" s="61" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="61">
-        <v>2</v>
-      </c>
-      <c r="B109" s="61" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="61">
-        <v>3</v>
-      </c>
-      <c r="B110" s="61" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="61">
-        <v>4</v>
-      </c>
-      <c r="B111" s="61" t="s">
-        <v>2147</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="61">
-        <v>5</v>
-      </c>
-      <c r="B112" s="61" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="61">
-        <v>6</v>
-      </c>
-      <c r="B113" s="61" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="61">
-        <v>7</v>
-      </c>
-      <c r="B114" s="61" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="61">
-        <v>8</v>
-      </c>
-      <c r="B115" s="61" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="61">
-        <v>9</v>
-      </c>
-      <c r="B116" s="61" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="61">
-        <v>10</v>
-      </c>
-      <c r="B117" s="61" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="61">
-        <v>11</v>
-      </c>
-      <c r="B118" s="61" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="61">
-        <v>12</v>
-      </c>
-      <c r="B119" s="61" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="61">
-        <v>13</v>
-      </c>
-      <c r="B120" s="61" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="61">
-        <v>14</v>
-      </c>
-      <c r="B121" s="61" t="s">
-        <v>2157</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="61">
-        <v>15</v>
-      </c>
-      <c r="B122" s="61" t="s">
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="61">
-        <v>16</v>
-      </c>
-      <c r="B123" s="61" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="61">
-        <v>17</v>
-      </c>
-      <c r="B124" s="61" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="61">
-        <v>18</v>
-      </c>
-      <c r="B125" s="61" t="s">
-        <v>2161</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="61">
-        <v>19</v>
-      </c>
-      <c r="B126" s="61" t="s">
-        <v>2162</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="61">
-        <v>20</v>
-      </c>
-      <c r="B127" s="61" t="s">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="B128" s="62" t="s">
-        <v>2164</v>
+      <c r="B129" s="60" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="60">
+      <c r="A130" s="60">
+        <v>22</v>
+      </c>
+      <c r="B130" s="60" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="345">
+      <c r="A131" s="60">
+        <v>23</v>
+      </c>
+      <c r="B131" s="63" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="120">
+      <c r="A132" s="60">
+        <v>24</v>
+      </c>
+      <c r="B132" s="63" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="B133" s="63" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>2183</v>
       </c>
     </row>
   </sheetData>
